--- a/artfynd/A 29597-2025 artfynd.xlsx
+++ b/artfynd/A 29597-2025 artfynd.xlsx
@@ -1588,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130000074</v>
+        <v>130000059</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>80192</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1599,21 +1599,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629737</v>
+        <v>630186</v>
       </c>
       <c r="R10" t="n">
-        <v>6991049</v>
+        <v>6991220</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,17 +1676,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1704,10 +1704,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130000059</v>
+        <v>130000074</v>
       </c>
       <c r="B11" t="n">
-        <v>80192</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,21 +1715,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630186</v>
+        <v>629737</v>
       </c>
       <c r="R11" t="n">
-        <v>6991220</v>
+        <v>6991049</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,17 +1792,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130000068</v>
+        <v>130000073</v>
       </c>
       <c r="B21" t="n">
         <v>79087</v>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>630134</v>
+        <v>629842</v>
       </c>
       <c r="R21" t="n">
-        <v>6991217</v>
+        <v>6991149</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130000073</v>
+        <v>130000053</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>57898</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2951,37 +2951,50 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>629842</v>
+        <v>629967</v>
       </c>
       <c r="R22" t="n">
-        <v>6991149</v>
+        <v>6991181</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3011,35 +3024,29 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3056,10 +3063,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130000053</v>
+        <v>130000068</v>
       </c>
       <c r="B23" t="n">
-        <v>57898</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3067,50 +3074,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>629967</v>
+        <v>630134</v>
       </c>
       <c r="R23" t="n">
-        <v>6991181</v>
+        <v>6991217</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3140,29 +3134,35 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">

--- a/artfynd/A 29597-2025 artfynd.xlsx
+++ b/artfynd/A 29597-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130000076</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>130000067</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>130000071</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>130000072</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>130000066</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>130000075</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>130000054</v>
       </c>
       <c r="B8" t="n">
-        <v>91616</v>
+        <v>91617</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>130000063</v>
       </c>
       <c r="B9" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>130000059</v>
       </c>
       <c r="B10" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>130000074</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>130000069</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>130000058</v>
       </c>
       <c r="B13" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>130000050</v>
       </c>
       <c r="B14" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>130000077</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>130000062</v>
       </c>
       <c r="B16" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>130000060</v>
       </c>
       <c r="B17" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>130000061</v>
       </c>
       <c r="B18" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>130000051</v>
       </c>
       <c r="B19" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>130000070</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130000073</v>
+        <v>130000053</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>57898</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2835,37 +2835,50 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>629842</v>
+        <v>629967</v>
       </c>
       <c r="R21" t="n">
-        <v>6991149</v>
+        <v>6991181</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2895,35 +2908,29 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2940,10 +2947,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130000053</v>
+        <v>130000068</v>
       </c>
       <c r="B22" t="n">
-        <v>57898</v>
+        <v>79088</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2951,50 +2958,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>629967</v>
+        <v>630134</v>
       </c>
       <c r="R22" t="n">
-        <v>6991181</v>
+        <v>6991217</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3024,29 +3018,35 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3063,10 +3063,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130000068</v>
+        <v>130000073</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630134</v>
+        <v>629842</v>
       </c>
       <c r="R23" t="n">
-        <v>6991217</v>
+        <v>6991149</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 29597-2025 artfynd.xlsx
+++ b/artfynd/A 29597-2025 artfynd.xlsx
@@ -1371,32 +1371,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130000054</v>
+        <v>130000063</v>
       </c>
       <c r="B8" t="n">
-        <v>91617</v>
+        <v>80193</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1412,7 +1412,7 @@
         <v>630184</v>
       </c>
       <c r="R8" t="n">
-        <v>6991226</v>
+        <v>6991231</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,6 +1456,21 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1472,32 +1487,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130000063</v>
+        <v>130000054</v>
       </c>
       <c r="B9" t="n">
-        <v>80193</v>
+        <v>91617</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1513,7 +1528,7 @@
         <v>630184</v>
       </c>
       <c r="R9" t="n">
-        <v>6991231</v>
+        <v>6991226</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,21 +1572,6 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -2824,10 +2824,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130000053</v>
+        <v>130000068</v>
       </c>
       <c r="B21" t="n">
-        <v>57898</v>
+        <v>79088</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2835,50 +2835,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>629967</v>
+        <v>630134</v>
       </c>
       <c r="R21" t="n">
-        <v>6991181</v>
+        <v>6991217</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2908,29 +2895,35 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2947,7 +2940,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130000068</v>
+        <v>130000073</v>
       </c>
       <c r="B22" t="n">
         <v>79088</v>
@@ -2985,10 +2978,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>630134</v>
+        <v>629842</v>
       </c>
       <c r="R22" t="n">
-        <v>6991217</v>
+        <v>6991149</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3063,10 +3056,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130000073</v>
+        <v>130000053</v>
       </c>
       <c r="B23" t="n">
-        <v>79088</v>
+        <v>57898</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3074,37 +3067,50 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>629842</v>
+        <v>629967</v>
       </c>
       <c r="R23" t="n">
-        <v>6991149</v>
+        <v>6991181</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3134,35 +3140,29 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">

--- a/artfynd/A 29597-2025 artfynd.xlsx
+++ b/artfynd/A 29597-2025 artfynd.xlsx
@@ -1371,32 +1371,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130000063</v>
+        <v>130000054</v>
       </c>
       <c r="B8" t="n">
-        <v>80193</v>
+        <v>91617</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1412,7 +1412,7 @@
         <v>630184</v>
       </c>
       <c r="R8" t="n">
-        <v>6991231</v>
+        <v>6991226</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,21 +1456,6 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1487,32 +1472,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130000054</v>
+        <v>130000063</v>
       </c>
       <c r="B9" t="n">
-        <v>91617</v>
+        <v>80193</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1528,7 +1513,7 @@
         <v>630184</v>
       </c>
       <c r="R9" t="n">
-        <v>6991226</v>
+        <v>6991231</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,6 +1557,21 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -2824,10 +2824,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130000068</v>
+        <v>130000053</v>
       </c>
       <c r="B21" t="n">
-        <v>79088</v>
+        <v>57898</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2835,37 +2835,50 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>630134</v>
+        <v>629967</v>
       </c>
       <c r="R21" t="n">
-        <v>6991217</v>
+        <v>6991181</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2895,35 +2908,29 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2940,7 +2947,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130000073</v>
+        <v>130000068</v>
       </c>
       <c r="B22" t="n">
         <v>79088</v>
@@ -2978,10 +2985,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>629842</v>
+        <v>630134</v>
       </c>
       <c r="R22" t="n">
-        <v>6991149</v>
+        <v>6991217</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3056,10 +3063,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130000053</v>
+        <v>130000073</v>
       </c>
       <c r="B23" t="n">
-        <v>57898</v>
+        <v>79088</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3067,50 +3074,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>629967</v>
+        <v>629842</v>
       </c>
       <c r="R23" t="n">
-        <v>6991181</v>
+        <v>6991149</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3140,29 +3134,35 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">

--- a/artfynd/A 29597-2025 artfynd.xlsx
+++ b/artfynd/A 29597-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130000076</v>
       </c>
       <c r="B2" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>130000067</v>
       </c>
       <c r="B3" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>130000071</v>
       </c>
       <c r="B4" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>130000072</v>
       </c>
       <c r="B5" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>130000066</v>
       </c>
       <c r="B6" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>130000075</v>
       </c>
       <c r="B7" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>130000054</v>
       </c>
       <c r="B8" t="n">
-        <v>91617</v>
+        <v>91634</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>130000063</v>
       </c>
       <c r="B9" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>130000059</v>
       </c>
       <c r="B10" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>130000074</v>
       </c>
       <c r="B11" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>130000069</v>
       </c>
       <c r="B12" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>130000058</v>
       </c>
       <c r="B13" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>130000050</v>
       </c>
       <c r="B14" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>130000077</v>
       </c>
       <c r="B15" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>130000062</v>
       </c>
       <c r="B16" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>130000060</v>
       </c>
       <c r="B17" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>130000061</v>
       </c>
       <c r="B18" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>130000051</v>
       </c>
       <c r="B19" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>130000070</v>
       </c>
       <c r="B20" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130000053</v>
+        <v>130000068</v>
       </c>
       <c r="B21" t="n">
-        <v>57898</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2835,50 +2835,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>629967</v>
+        <v>630134</v>
       </c>
       <c r="R21" t="n">
-        <v>6991181</v>
+        <v>6991217</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2908,29 +2895,35 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2947,10 +2940,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130000068</v>
+        <v>130000073</v>
       </c>
       <c r="B22" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2985,10 +2978,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>630134</v>
+        <v>629842</v>
       </c>
       <c r="R22" t="n">
-        <v>6991217</v>
+        <v>6991149</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3063,10 +3056,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130000073</v>
+        <v>130000053</v>
       </c>
       <c r="B23" t="n">
-        <v>79088</v>
+        <v>57899</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3074,37 +3067,50 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>629842</v>
+        <v>629967</v>
       </c>
       <c r="R23" t="n">
-        <v>6991149</v>
+        <v>6991181</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3134,35 +3140,29 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">

--- a/artfynd/A 29597-2025 artfynd.xlsx
+++ b/artfynd/A 29597-2025 artfynd.xlsx
@@ -1588,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130000074</v>
+        <v>130000059</v>
       </c>
       <c r="B10" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1599,21 +1599,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629737</v>
+        <v>630186</v>
       </c>
       <c r="R10" t="n">
-        <v>6991049</v>
+        <v>6991220</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,17 +1676,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1704,10 +1704,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130000059</v>
+        <v>130000074</v>
       </c>
       <c r="B11" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,21 +1715,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630186</v>
+        <v>629737</v>
       </c>
       <c r="R11" t="n">
-        <v>6991220</v>
+        <v>6991049</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,17 +1792,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -3179,61 +3179,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130108885</v>
+        <v>130108898</v>
       </c>
       <c r="B24" t="n">
-        <v>56931</v>
+        <v>79095</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630313</v>
+        <v>630253</v>
       </c>
       <c r="R24" t="n">
-        <v>6991284</v>
+        <v>6991255</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3265,7 +3252,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3275,7 +3262,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3284,8 +3271,24 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3302,48 +3305,61 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130108898</v>
+        <v>130108885</v>
       </c>
       <c r="B25" t="n">
-        <v>79095</v>
+        <v>56931</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>630253</v>
+        <v>630313</v>
       </c>
       <c r="R25" t="n">
-        <v>6991255</v>
+        <v>6991284</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3375,7 +3391,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3385,7 +3401,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3394,24 +3410,8 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">

--- a/artfynd/A 29597-2025 artfynd.xlsx
+++ b/artfynd/A 29597-2025 artfynd.xlsx
@@ -1490,7 +1490,7 @@
         <v>130000054</v>
       </c>
       <c r="B9" t="n">
-        <v>91650</v>
+        <v>91652</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>130000050</v>
       </c>
       <c r="B14" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>130000051</v>
       </c>
       <c r="B19" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>130108889</v>
       </c>
       <c r="B29" t="n">
-        <v>91937</v>
+        <v>91939</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>130108887</v>
       </c>
       <c r="B30" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>130108891</v>
       </c>
       <c r="B31" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>130108881</v>
       </c>
       <c r="B34" t="n">
-        <v>91562</v>
+        <v>91564</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 29597-2025 artfynd.xlsx
+++ b/artfynd/A 29597-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130000076</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>130000067</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>130000071</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>130000072</v>
       </c>
       <c r="B5" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>130000066</v>
       </c>
       <c r="B6" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>130000075</v>
       </c>
       <c r="B7" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,32 +1371,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130000063</v>
+        <v>130000054</v>
       </c>
       <c r="B8" t="n">
-        <v>80200</v>
+        <v>91739</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1412,7 +1412,7 @@
         <v>630184</v>
       </c>
       <c r="R8" t="n">
-        <v>6991231</v>
+        <v>6991226</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,21 +1456,6 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1487,32 +1472,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130000054</v>
+        <v>130000063</v>
       </c>
       <c r="B9" t="n">
-        <v>91652</v>
+        <v>80285</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1528,7 +1513,7 @@
         <v>630184</v>
       </c>
       <c r="R9" t="n">
-        <v>6991226</v>
+        <v>6991231</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,6 +1557,21 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1588,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130000059</v>
+        <v>130000074</v>
       </c>
       <c r="B10" t="n">
-        <v>80200</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1599,21 +1599,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>630186</v>
+        <v>629737</v>
       </c>
       <c r="R10" t="n">
-        <v>6991220</v>
+        <v>6991049</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,17 +1676,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1704,10 +1704,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130000074</v>
+        <v>130000059</v>
       </c>
       <c r="B11" t="n">
-        <v>79095</v>
+        <v>80285</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,21 +1715,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629737</v>
+        <v>630186</v>
       </c>
       <c r="R11" t="n">
-        <v>6991049</v>
+        <v>6991220</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,17 +1792,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1823,7 +1823,7 @@
         <v>130000069</v>
       </c>
       <c r="B12" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>130000058</v>
       </c>
       <c r="B13" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>130000050</v>
       </c>
       <c r="B14" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>130000077</v>
       </c>
       <c r="B15" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>130000062</v>
       </c>
       <c r="B16" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>130000060</v>
       </c>
       <c r="B17" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>130000061</v>
       </c>
       <c r="B18" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>130000051</v>
       </c>
       <c r="B19" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>130000070</v>
       </c>
       <c r="B20" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>130000068</v>
       </c>
       <c r="B21" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>130000073</v>
       </c>
       <c r="B22" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>130000053</v>
       </c>
       <c r="B23" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>130108898</v>
       </c>
       <c r="B24" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>130108885</v>
       </c>
       <c r="B25" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>130108886</v>
       </c>
       <c r="B26" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>130108896</v>
       </c>
       <c r="B27" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>130108890</v>
       </c>
       <c r="B28" t="n">
-        <v>80228</v>
+        <v>80313</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>130108889</v>
       </c>
       <c r="B29" t="n">
-        <v>91939</v>
+        <v>92026</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>130108887</v>
       </c>
       <c r="B30" t="n">
-        <v>92094</v>
+        <v>92181</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>130108891</v>
       </c>
       <c r="B31" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>130108894</v>
       </c>
       <c r="B32" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>130108895</v>
       </c>
       <c r="B33" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>130108881</v>
       </c>
       <c r="B34" t="n">
-        <v>91564</v>
+        <v>91651</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 29597-2025 artfynd.xlsx
+++ b/artfynd/A 29597-2025 artfynd.xlsx
@@ -1588,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130000074</v>
+        <v>130000059</v>
       </c>
       <c r="B10" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1599,21 +1599,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629737</v>
+        <v>630186</v>
       </c>
       <c r="R10" t="n">
-        <v>6991049</v>
+        <v>6991220</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,17 +1676,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1704,10 +1704,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130000059</v>
+        <v>130000074</v>
       </c>
       <c r="B11" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,21 +1715,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630186</v>
+        <v>629737</v>
       </c>
       <c r="R11" t="n">
-        <v>6991220</v>
+        <v>6991049</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,17 +1792,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 29597-2025 artfynd.xlsx
+++ b/artfynd/A 29597-2025 artfynd.xlsx
@@ -1588,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130000059</v>
+        <v>130000074</v>
       </c>
       <c r="B10" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1599,21 +1599,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>630186</v>
+        <v>629737</v>
       </c>
       <c r="R10" t="n">
-        <v>6991220</v>
+        <v>6991049</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,17 +1676,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1704,10 +1704,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130000074</v>
+        <v>130000059</v>
       </c>
       <c r="B11" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,21 +1715,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629737</v>
+        <v>630186</v>
       </c>
       <c r="R11" t="n">
-        <v>6991049</v>
+        <v>6991220</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,17 +1792,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 29597-2025 artfynd.xlsx
+++ b/artfynd/A 29597-2025 artfynd.xlsx
@@ -1371,32 +1371,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130000054</v>
+        <v>130000063</v>
       </c>
       <c r="B8" t="n">
-        <v>91739</v>
+        <v>80285</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1412,7 +1412,7 @@
         <v>630184</v>
       </c>
       <c r="R8" t="n">
-        <v>6991226</v>
+        <v>6991231</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,6 +1456,21 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1472,32 +1487,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130000063</v>
+        <v>130000054</v>
       </c>
       <c r="B9" t="n">
-        <v>80285</v>
+        <v>91739</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1513,7 +1528,7 @@
         <v>630184</v>
       </c>
       <c r="R9" t="n">
-        <v>6991231</v>
+        <v>6991226</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,21 +1572,6 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1588,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130000074</v>
+        <v>130000059</v>
       </c>
       <c r="B10" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1599,21 +1599,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629737</v>
+        <v>630186</v>
       </c>
       <c r="R10" t="n">
-        <v>6991049</v>
+        <v>6991220</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,17 +1676,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1704,10 +1704,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130000059</v>
+        <v>130000074</v>
       </c>
       <c r="B11" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,21 +1715,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630186</v>
+        <v>629737</v>
       </c>
       <c r="R11" t="n">
-        <v>6991220</v>
+        <v>6991049</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,17 +1792,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -3179,48 +3179,61 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130108898</v>
+        <v>130108885</v>
       </c>
       <c r="B24" t="n">
-        <v>79180</v>
+        <v>57016</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630253</v>
+        <v>630313</v>
       </c>
       <c r="R24" t="n">
-        <v>6991255</v>
+        <v>6991284</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3252,7 +3265,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3262,7 +3275,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3271,24 +3284,8 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3305,61 +3302,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130108885</v>
+        <v>130108898</v>
       </c>
       <c r="B25" t="n">
-        <v>57016</v>
+        <v>79180</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>630313</v>
+        <v>630253</v>
       </c>
       <c r="R25" t="n">
-        <v>6991284</v>
+        <v>6991255</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3391,7 +3375,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3401,7 +3385,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3410,8 +3394,24 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">

--- a/artfynd/A 29597-2025 artfynd.xlsx
+++ b/artfynd/A 29597-2025 artfynd.xlsx
@@ -1588,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130000059</v>
+        <v>130000074</v>
       </c>
       <c r="B10" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1599,21 +1599,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>630186</v>
+        <v>629737</v>
       </c>
       <c r="R10" t="n">
-        <v>6991220</v>
+        <v>6991049</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,17 +1676,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1704,10 +1704,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130000074</v>
+        <v>130000059</v>
       </c>
       <c r="B11" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,21 +1715,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629737</v>
+        <v>630186</v>
       </c>
       <c r="R11" t="n">
-        <v>6991049</v>
+        <v>6991220</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,17 +1792,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130000068</v>
+        <v>130000053</v>
       </c>
       <c r="B21" t="n">
-        <v>79180</v>
+        <v>57985</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2835,37 +2835,50 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>630134</v>
+        <v>629967</v>
       </c>
       <c r="R21" t="n">
-        <v>6991217</v>
+        <v>6991181</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2895,35 +2908,29 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2940,7 +2947,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130000073</v>
+        <v>130000068</v>
       </c>
       <c r="B22" t="n">
         <v>79180</v>
@@ -2978,10 +2985,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>629842</v>
+        <v>630134</v>
       </c>
       <c r="R22" t="n">
-        <v>6991149</v>
+        <v>6991217</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3056,10 +3063,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130000053</v>
+        <v>130000073</v>
       </c>
       <c r="B23" t="n">
-        <v>57985</v>
+        <v>79180</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3067,50 +3074,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Andersmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>629967</v>
+        <v>629842</v>
       </c>
       <c r="R23" t="n">
-        <v>6991181</v>
+        <v>6991149</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3140,29 +3134,35 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">

--- a/artfynd/A 29597-2025 artfynd.xlsx
+++ b/artfynd/A 29597-2025 artfynd.xlsx
@@ -3182,7 +3182,7 @@
         <v>130108898</v>
       </c>
       <c r="B24" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>130108896</v>
       </c>
       <c r="B27" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>130108890</v>
       </c>
       <c r="B28" t="n">
-        <v>80313</v>
+        <v>80316</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>130108889</v>
       </c>
       <c r="B29" t="n">
-        <v>92026</v>
+        <v>92029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>130108887</v>
       </c>
       <c r="B30" t="n">
-        <v>92181</v>
+        <v>92184</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>130108891</v>
       </c>
       <c r="B31" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>130108894</v>
       </c>
       <c r="B32" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>130108895</v>
       </c>
       <c r="B33" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>130108881</v>
       </c>
       <c r="B34" t="n">
-        <v>91651</v>
+        <v>91654</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 29597-2025 artfynd.xlsx
+++ b/artfynd/A 29597-2025 artfynd.xlsx
@@ -3182,7 +3182,7 @@
         <v>130108898</v>
       </c>
       <c r="B24" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>130108885</v>
       </c>
       <c r="B25" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>130108886</v>
       </c>
       <c r="B26" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>130108896</v>
       </c>
       <c r="B27" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>130108890</v>
       </c>
       <c r="B28" t="n">
-        <v>80316</v>
+        <v>80342</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>130108889</v>
       </c>
       <c r="B29" t="n">
-        <v>92029</v>
+        <v>92055</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>130108887</v>
       </c>
       <c r="B30" t="n">
-        <v>92184</v>
+        <v>92210</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>130108891</v>
       </c>
       <c r="B31" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>130108894</v>
       </c>
       <c r="B32" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>130108895</v>
       </c>
       <c r="B33" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>130108881</v>
       </c>
       <c r="B34" t="n">
-        <v>91654</v>
+        <v>91680</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
